--- a/Dowling/dowling-vs-dcg-offense.xlsx
+++ b/Dowling/dowling-vs-dcg-offense.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R3e390126ece0421f"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R8eea257376ae4987"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -227,6 +242,9 @@
   </si>
   <si>
     <t>LUKE/RICK</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>MIRROR PATRIOTS TEAL</t>
@@ -293,7 +311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X151"/>
+  <dimension ref="A1:AC151"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -368,6 +386,21 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -377,7 +410,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -386,13 +419,13 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -403,7 +436,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -412,13 +445,13 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -429,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -438,13 +471,13 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -455,7 +488,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -464,13 +497,13 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +514,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -490,13 +523,13 @@
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -507,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -516,13 +549,13 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +566,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -542,13 +575,13 @@
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +592,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -568,13 +601,13 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -585,7 +618,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -594,13 +627,13 @@
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -611,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -620,13 +653,13 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -637,7 +670,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -646,13 +679,13 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -663,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -672,13 +705,13 @@
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -689,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -698,13 +731,13 @@
         <v>10</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -724,13 +757,13 @@
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -741,7 +774,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -750,13 +783,13 @@
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -776,13 +809,13 @@
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -793,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -802,13 +835,13 @@
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I18" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -819,7 +852,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -828,13 +861,13 @@
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -845,7 +878,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -854,25 +887,28 @@
         <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>39</v>
-      </c>
-      <c r="S20" t="s">
-        <v>40</v>
-      </c>
-      <c r="T20" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="X20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -892,25 +928,25 @@
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J21">
         <v>7</v>
       </c>
       <c r="K21" t="s">
-        <v>42</v>
-      </c>
-      <c r="S21" t="s">
-        <v>43</v>
-      </c>
-      <c r="T21" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="X21" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -921,34 +957,37 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" t="s">
         <v>38</v>
       </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="G22" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>33</v>
-      </c>
       <c r="J22">
         <v>10</v>
       </c>
       <c r="K22" t="s">
-        <v>42</v>
-      </c>
-      <c r="S22" t="s">
-        <v>45</v>
-      </c>
-      <c r="T22" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="X22" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -959,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -968,25 +1007,28 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>39</v>
-      </c>
-      <c r="S23" t="s">
-        <v>47</v>
-      </c>
-      <c r="T23" t="s">
-        <v>48</v>
+        <v>44</v>
+      </c>
+      <c r="X23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -997,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1006,25 +1048,25 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>39</v>
-      </c>
-      <c r="S24" t="s">
-        <v>49</v>
-      </c>
-      <c r="T24" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="X24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1035,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1044,25 +1086,28 @@
         <v>10</v>
       </c>
       <c r="G25" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J25">
         <v>-10</v>
       </c>
       <c r="K25" t="s">
-        <v>39</v>
-      </c>
-      <c r="S25" t="s">
-        <v>52</v>
-      </c>
-      <c r="T25" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="X25" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -1073,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -1082,13 +1127,13 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1099,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1108,13 +1153,13 @@
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -1125,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1134,13 +1179,13 @@
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1151,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -1160,13 +1205,13 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -1177,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1186,13 +1231,13 @@
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -1203,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -1212,13 +1257,13 @@
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
@@ -1229,34 +1274,37 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" t="s">
         <v>38</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>10</v>
-      </c>
-      <c r="G32" t="s">
-        <v>29</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" t="s">
-        <v>33</v>
       </c>
       <c r="J32">
         <v>8</v>
       </c>
       <c r="K32" t="s">
-        <v>42</v>
-      </c>
-      <c r="S32" t="s">
-        <v>40</v>
-      </c>
-      <c r="T32" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="P32" t="s">
+        <v>29</v>
+      </c>
+      <c r="X32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33">
@@ -1267,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -1276,25 +1324,25 @@
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J33">
         <v>14</v>
       </c>
       <c r="K33" t="s">
-        <v>42</v>
-      </c>
-      <c r="S33" t="s">
         <v>47</v>
       </c>
-      <c r="T33" t="s">
-        <v>57</v>
+      <c r="X33" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34">
@@ -1305,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1314,25 +1362,28 @@
         <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J34">
         <v>17</v>
       </c>
       <c r="K34" t="s">
-        <v>42</v>
-      </c>
-      <c r="S34" t="s">
-        <v>58</v>
-      </c>
-      <c r="T34" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="P34" t="s">
+        <v>29</v>
+      </c>
+      <c r="X34" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="35">
@@ -1343,34 +1394,37 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" t="s">
         <v>38</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-      <c r="G35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" t="s">
-        <v>33</v>
       </c>
       <c r="J35">
         <v>5</v>
       </c>
       <c r="K35" t="s">
-        <v>42</v>
-      </c>
-      <c r="S35" t="s">
-        <v>58</v>
-      </c>
-      <c r="T35" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="P35" t="s">
+        <v>29</v>
+      </c>
+      <c r="X35" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -1381,7 +1435,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -1390,25 +1444,28 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J36">
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
-      </c>
-      <c r="S36" t="s">
-        <v>40</v>
-      </c>
-      <c r="T36" t="s">
-        <v>59</v>
+        <v>44</v>
+      </c>
+      <c r="P36" t="s">
+        <v>29</v>
+      </c>
+      <c r="X36" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="37">
@@ -1419,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -1428,25 +1485,25 @@
         <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I37" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J37">
         <v>12</v>
       </c>
       <c r="K37" t="s">
-        <v>42</v>
-      </c>
-      <c r="S37" t="s">
-        <v>43</v>
-      </c>
-      <c r="T37" t="s">
-        <v>61</v>
+        <v>47</v>
+      </c>
+      <c r="X37" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="38">
@@ -1457,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1466,25 +1523,25 @@
         <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I38" t="s">
+        <v>67</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38" t="s">
+        <v>47</v>
+      </c>
+      <c r="X38" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y38" t="s">
         <v>62</v>
-      </c>
-      <c r="J38">
-        <v>3</v>
-      </c>
-      <c r="K38" t="s">
-        <v>42</v>
-      </c>
-      <c r="S38" t="s">
-        <v>43</v>
-      </c>
-      <c r="T38" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -1495,7 +1552,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1507,13 +1564,13 @@
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I39" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
@@ -1524,7 +1581,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1533,13 +1590,13 @@
         <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I40" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -1550,7 +1607,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1559,13 +1616,13 @@
         <v>10</v>
       </c>
       <c r="G41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
@@ -1576,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -1585,13 +1642,13 @@
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -1602,7 +1659,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1611,13 +1668,13 @@
         <v>10</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -1628,7 +1685,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1637,13 +1694,13 @@
         <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -1654,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -1663,13 +1720,13 @@
         <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -1680,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -1689,15 +1746,15 @@
         <v>7</v>
       </c>
       <c r="G46" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
-        <v>55</v>
-      </c>
-      <c r="W46">
+        <v>60</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -1709,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1718,18 +1775,18 @@
         <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I47" t="s">
-        <v>65</v>
-      </c>
-      <c r="S47" t="s">
-        <v>47</v>
-      </c>
-      <c r="T47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W47">
+        <v>70</v>
+      </c>
+      <c r="X47" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -1741,7 +1798,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1750,27 +1807,27 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J48">
         <v>4</v>
       </c>
       <c r="K48" t="s">
-        <v>42</v>
-      </c>
-      <c r="S48" t="s">
-        <v>67</v>
-      </c>
-      <c r="T48" t="s">
-        <v>68</v>
-      </c>
-      <c r="W48">
+        <v>47</v>
+      </c>
+      <c r="X48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -1782,7 +1839,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1791,25 +1848,28 @@
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H49" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J49">
         <v>6</v>
       </c>
       <c r="K49" t="s">
-        <v>42</v>
-      </c>
-      <c r="S49" t="s">
-        <v>69</v>
-      </c>
-      <c r="T49" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+      <c r="X49" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="50">
@@ -1820,7 +1880,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -1829,25 +1889,25 @@
         <v>6</v>
       </c>
       <c r="G50" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H50" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J50">
         <v>4</v>
       </c>
       <c r="K50" t="s">
-        <v>39</v>
-      </c>
-      <c r="S50" t="s">
-        <v>43</v>
-      </c>
-      <c r="T50" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="X50" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="51">
@@ -1858,7 +1918,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -1867,13 +1927,13 @@
         <v>3</v>
       </c>
       <c r="G51" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I51" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52">
@@ -1884,7 +1944,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1893,13 +1953,13 @@
         <v>10</v>
       </c>
       <c r="G52" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H52" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53">
@@ -1910,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -1919,13 +1979,13 @@
         <v>3</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54">
@@ -1936,7 +1996,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -1945,13 +2005,13 @@
         <v>3</v>
       </c>
       <c r="G54" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -1962,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -1971,13 +2031,13 @@
         <v>3</v>
       </c>
       <c r="G55" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I55" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56">
@@ -1988,7 +2048,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1997,25 +2057,25 @@
         <v>10</v>
       </c>
       <c r="G56" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J56">
         <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>42</v>
-      </c>
-      <c r="S56" t="s">
         <v>47</v>
       </c>
-      <c r="T56" t="s">
-        <v>66</v>
+      <c r="X56" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="57">
@@ -2026,7 +2086,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2035,25 +2095,25 @@
         <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I57" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J57">
         <v>9</v>
       </c>
       <c r="K57" t="s">
-        <v>42</v>
-      </c>
-      <c r="S57" t="s">
-        <v>71</v>
-      </c>
-      <c r="T57" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="X57" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="58">
@@ -2064,34 +2124,37 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="G58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" t="s">
+        <v>37</v>
+      </c>
+      <c r="I58" t="s">
         <v>38</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58">
-        <v>10</v>
-      </c>
-      <c r="G58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" t="s">
-        <v>33</v>
       </c>
       <c r="J58">
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>42</v>
-      </c>
-      <c r="S58" t="s">
-        <v>40</v>
-      </c>
-      <c r="T58" t="s">
-        <v>72</v>
+        <v>47</v>
+      </c>
+      <c r="P58" t="s">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="59">
@@ -2102,34 +2165,37 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>10</v>
+      </c>
+      <c r="G59" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" t="s">
+        <v>37</v>
+      </c>
+      <c r="I59" t="s">
         <v>38</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>10</v>
-      </c>
-      <c r="G59" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" t="s">
-        <v>33</v>
       </c>
       <c r="J59">
         <v>8</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
-      </c>
-      <c r="S59" t="s">
-        <v>69</v>
-      </c>
-      <c r="T59" t="s">
-        <v>73</v>
+        <v>47</v>
+      </c>
+      <c r="P59" t="s">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60">
@@ -2140,7 +2206,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -2149,25 +2215,25 @@
         <v>4</v>
       </c>
       <c r="G60" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J60">
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
-      </c>
-      <c r="S60" t="s">
-        <v>69</v>
-      </c>
-      <c r="T60" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X60" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="61">
@@ -2178,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D61">
         <v>3</v>
@@ -2190,25 +2256,25 @@
         <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J61">
         <v>4</v>
       </c>
       <c r="K61" t="s">
-        <v>42</v>
-      </c>
-      <c r="S61" t="s">
-        <v>74</v>
-      </c>
-      <c r="T61" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="X61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="62">
@@ -2219,7 +2285,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2231,25 +2297,28 @@
         <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I62" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>39</v>
-      </c>
-      <c r="S62" t="s">
-        <v>40</v>
-      </c>
-      <c r="T62" t="s">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="P62" t="s">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="63">
@@ -2260,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2272,25 +2341,25 @@
         <v>38</v>
       </c>
       <c r="G63" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J63">
         <v>43</v>
       </c>
       <c r="K63" t="s">
-        <v>42</v>
-      </c>
-      <c r="S63" t="s">
-        <v>75</v>
-      </c>
-      <c r="T63" t="s">
-        <v>76</v>
+        <v>47</v>
+      </c>
+      <c r="X63" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="64">
@@ -2301,7 +2370,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2313,25 +2382,28 @@
         <v>-5</v>
       </c>
       <c r="G64" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I64" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>42</v>
-      </c>
-      <c r="S64" t="s">
-        <v>58</v>
-      </c>
-      <c r="T64" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="P64" t="s">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="65">
@@ -2342,7 +2414,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -2351,25 +2423,25 @@
         <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J65">
         <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>42</v>
-      </c>
-      <c r="S65" t="s">
-        <v>71</v>
-      </c>
-      <c r="T65" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="X65" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -2380,7 +2452,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2392,13 +2464,13 @@
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H66" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I66" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
@@ -2409,7 +2481,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -2418,13 +2490,13 @@
         <v>10</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H67" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -2435,7 +2507,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -2444,13 +2516,13 @@
         <v>10</v>
       </c>
       <c r="G68" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I68" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -2461,7 +2533,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -2470,16 +2542,16 @@
         <v>10</v>
       </c>
       <c r="G69" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H69" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I69" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70">
@@ -2490,7 +2562,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2499,25 +2571,25 @@
         <v>10</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
-      </c>
-      <c r="S70" t="s">
-        <v>67</v>
-      </c>
-      <c r="T70" t="s">
         <v>44</v>
+      </c>
+      <c r="X70" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="71">
@@ -2528,34 +2600,34 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+      <c r="G71" t="s">
+        <v>30</v>
+      </c>
+      <c r="H71" t="s">
+        <v>37</v>
+      </c>
+      <c r="I71" t="s">
         <v>38</v>
       </c>
-      <c r="D71">
-        <v>2</v>
-      </c>
-      <c r="E71">
-        <v>10</v>
-      </c>
-      <c r="G71" t="s">
-        <v>25</v>
-      </c>
-      <c r="H71" t="s">
-        <v>32</v>
-      </c>
-      <c r="I71" t="s">
-        <v>33</v>
-      </c>
       <c r="J71">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
-      </c>
-      <c r="S71" t="s">
-        <v>58</v>
-      </c>
-      <c r="T71" t="s">
-        <v>79</v>
+        <v>44</v>
+      </c>
+      <c r="X71" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="72">
@@ -2566,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -2575,25 +2647,25 @@
         <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I72" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>39</v>
-      </c>
-      <c r="S72" t="s">
-        <v>40</v>
-      </c>
-      <c r="T72" t="s">
-        <v>80</v>
+        <v>44</v>
+      </c>
+      <c r="X72" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="73">
@@ -2604,7 +2676,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -2613,13 +2685,13 @@
         <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H73" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I73" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
@@ -2630,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -2639,13 +2711,13 @@
         <v>10</v>
       </c>
       <c r="G74" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H74" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75">
@@ -2656,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -2665,13 +2737,13 @@
         <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H75" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76">
@@ -2682,7 +2754,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -2691,13 +2763,13 @@
         <v>10</v>
       </c>
       <c r="G76" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I76" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77">
@@ -2708,7 +2780,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -2717,25 +2789,25 @@
         <v>10</v>
       </c>
       <c r="G77" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H77" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J77">
         <v>6</v>
       </c>
       <c r="K77" t="s">
-        <v>42</v>
-      </c>
-      <c r="S77" t="s">
         <v>47</v>
       </c>
-      <c r="T77" t="s">
-        <v>66</v>
+      <c r="X77" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="78">
@@ -2746,7 +2818,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -2755,27 +2827,27 @@
         <v>4</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>39</v>
-      </c>
-      <c r="S78" t="s">
-        <v>43</v>
-      </c>
-      <c r="T78" t="s">
-        <v>61</v>
-      </c>
-      <c r="W78">
+        <v>44</v>
+      </c>
+      <c r="X78" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -2787,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -2796,15 +2868,15 @@
         <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I79" t="s">
-        <v>65</v>
-      </c>
-      <c r="S79" t="s">
-        <v>69</v>
-      </c>
-      <c r="W79">
+        <v>70</v>
+      </c>
+      <c r="X79" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -2816,7 +2888,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -2825,27 +2897,27 @@
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J80">
         <v>7</v>
       </c>
       <c r="K80" t="s">
-        <v>42</v>
-      </c>
-      <c r="S80" t="s">
-        <v>82</v>
-      </c>
-      <c r="T80" t="s">
-        <v>83</v>
-      </c>
-      <c r="W80">
+        <v>47</v>
+      </c>
+      <c r="X80" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB80">
         <v>5</v>
       </c>
     </row>
@@ -2857,7 +2929,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -2866,25 +2938,28 @@
         <v>8</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H81" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I81" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
-      </c>
-      <c r="S81" t="s">
-        <v>75</v>
-      </c>
-      <c r="T81" t="s">
-        <v>46</v>
+        <v>44</v>
+      </c>
+      <c r="P81" t="s">
+        <v>29</v>
+      </c>
+      <c r="X81" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="82">
@@ -2895,7 +2970,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -2904,13 +2979,13 @@
         <v>8</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I82" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83">
@@ -2921,7 +2996,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2930,13 +3005,13 @@
         <v>10</v>
       </c>
       <c r="G83" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I83" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84">
@@ -2947,7 +3022,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -2956,13 +3031,13 @@
         <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I84" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="85">
@@ -2973,7 +3048,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -2982,13 +3057,13 @@
         <v>4</v>
       </c>
       <c r="G85" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I85" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86">
@@ -2999,7 +3074,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3008,13 +3083,13 @@
         <v>10</v>
       </c>
       <c r="G86" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I86" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87">
@@ -3025,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3034,13 +3109,13 @@
         <v>10</v>
       </c>
       <c r="G87" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I87" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
@@ -3051,7 +3126,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3060,13 +3135,13 @@
         <v>6</v>
       </c>
       <c r="G88" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H88" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I88" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
@@ -3077,7 +3152,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -3086,13 +3161,13 @@
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H89" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I89" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90">
@@ -3103,7 +3178,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -3112,13 +3187,13 @@
         <v>1</v>
       </c>
       <c r="G90" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I90" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91">
@@ -3129,7 +3204,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3138,13 +3213,13 @@
         <v>10</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H91" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92">
@@ -3155,7 +3230,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3164,13 +3239,13 @@
         <v>10</v>
       </c>
       <c r="G92" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I92" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93">
@@ -3181,7 +3256,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3190,13 +3265,13 @@
         <v>10</v>
       </c>
       <c r="G93" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I93" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94">
@@ -3207,7 +3282,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3216,25 +3291,25 @@
         <v>10</v>
       </c>
       <c r="G94" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>39</v>
-      </c>
-      <c r="S94" t="s">
-        <v>47</v>
-      </c>
-      <c r="T94" t="s">
-        <v>66</v>
+        <v>44</v>
+      </c>
+      <c r="X94" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="95">
@@ -3245,34 +3320,34 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95" t="s">
+        <v>37</v>
+      </c>
+      <c r="I95" t="s">
         <v>38</v>
-      </c>
-      <c r="D95">
-        <v>2</v>
-      </c>
-      <c r="E95">
-        <v>10</v>
-      </c>
-      <c r="G95" t="s">
-        <v>25</v>
-      </c>
-      <c r="H95" t="s">
-        <v>32</v>
-      </c>
-      <c r="I95" t="s">
-        <v>33</v>
       </c>
       <c r="J95">
         <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>42</v>
-      </c>
-      <c r="S95" t="s">
-        <v>43</v>
-      </c>
-      <c r="T95" t="s">
-        <v>87</v>
+        <v>47</v>
+      </c>
+      <c r="X95" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="96">
@@ -3283,7 +3358,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3292,25 +3367,25 @@
         <v>10</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J96">
         <v>26</v>
       </c>
       <c r="K96" t="s">
-        <v>42</v>
-      </c>
-      <c r="S96" t="s">
-        <v>71</v>
-      </c>
-      <c r="T96" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X96" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="97">
@@ -3321,7 +3396,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3330,25 +3405,25 @@
         <v>10</v>
       </c>
       <c r="G97" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I97" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>10</v>
       </c>
       <c r="K97" t="s">
-        <v>42</v>
-      </c>
-      <c r="S97" t="s">
-        <v>71</v>
-      </c>
-      <c r="T97" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X97" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="98">
@@ -3359,7 +3434,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -3368,25 +3443,25 @@
         <v>1</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H98" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>39</v>
-      </c>
-      <c r="S98" t="s">
-        <v>71</v>
-      </c>
-      <c r="T98" t="s">
-        <v>68</v>
+        <v>44</v>
+      </c>
+      <c r="X98" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="99">
@@ -3397,7 +3472,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -3406,25 +3481,25 @@
         <v>2</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I99" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J99">
         <v>6</v>
       </c>
       <c r="K99" t="s">
-        <v>42</v>
-      </c>
-      <c r="S99" t="s">
-        <v>67</v>
-      </c>
-      <c r="T99" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="X99" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="100">
@@ -3435,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3444,25 +3519,25 @@
         <v>10</v>
       </c>
       <c r="G100" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J100">
         <v>12</v>
       </c>
       <c r="K100" t="s">
-        <v>42</v>
-      </c>
-      <c r="S100" t="s">
         <v>47</v>
       </c>
-      <c r="T100" t="s">
-        <v>57</v>
+      <c r="X100" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="101">
@@ -3473,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3482,25 +3557,25 @@
         <v>9</v>
       </c>
       <c r="G101" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J101">
         <v>6</v>
       </c>
       <c r="K101" t="s">
-        <v>42</v>
-      </c>
-      <c r="S101" t="s">
         <v>47</v>
       </c>
-      <c r="T101" t="s">
-        <v>57</v>
+      <c r="X101" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="102">
@@ -3511,7 +3586,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -3520,25 +3595,25 @@
         <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J102">
         <v>4</v>
       </c>
       <c r="K102" t="s">
-        <v>42</v>
-      </c>
-      <c r="S102" t="s">
-        <v>74</v>
-      </c>
-      <c r="T102" t="s">
-        <v>88</v>
+        <v>47</v>
+      </c>
+      <c r="X102" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="103">
@@ -3549,7 +3624,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3561,13 +3636,13 @@
         <v>3</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H103" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I103" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104">
@@ -3578,7 +3653,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3587,13 +3662,13 @@
         <v>10</v>
       </c>
       <c r="G104" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H104" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I104" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105">
@@ -3604,7 +3679,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3613,13 +3688,13 @@
         <v>10</v>
       </c>
       <c r="G105" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I105" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106">
@@ -3630,7 +3705,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3639,13 +3714,13 @@
         <v>10</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I106" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107">
@@ -3656,7 +3731,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3665,13 +3740,13 @@
         <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H107" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
@@ -3682,7 +3757,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -3691,13 +3766,13 @@
         <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I108" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
@@ -3708,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -3717,13 +3792,13 @@
         <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I109" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110">
@@ -3734,7 +3809,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -3743,13 +3818,13 @@
         <v>24</v>
       </c>
       <c r="G110" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H110" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I110" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111">
@@ -3760,7 +3835,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3769,25 +3844,25 @@
         <v>10</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H111" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J111">
         <v>5</v>
       </c>
       <c r="K111" t="s">
-        <v>42</v>
-      </c>
-      <c r="S111" t="s">
         <v>47</v>
       </c>
-      <c r="T111" t="s">
-        <v>57</v>
+      <c r="X111" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="112">
@@ -3798,7 +3873,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -3807,25 +3882,25 @@
         <v>6</v>
       </c>
       <c r="G112" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H112" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I112" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J112">
         <v>8</v>
       </c>
       <c r="K112" t="s">
-        <v>42</v>
-      </c>
-      <c r="S112" t="s">
-        <v>67</v>
-      </c>
-      <c r="T112" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X112" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="113">
@@ -3836,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3845,25 +3920,25 @@
         <v>10</v>
       </c>
       <c r="G113" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H113" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J113">
         <v>5</v>
       </c>
       <c r="K113" t="s">
-        <v>42</v>
-      </c>
-      <c r="S113" t="s">
         <v>47</v>
       </c>
-      <c r="T113" t="s">
-        <v>66</v>
+      <c r="X113" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="114">
@@ -3874,7 +3949,7 @@
         <v>3</v>
       </c>
       <c r="C114" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -3883,25 +3958,25 @@
         <v>6</v>
       </c>
       <c r="G114" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H114" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I114" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J114">
         <v>5</v>
       </c>
       <c r="K114" t="s">
-        <v>42</v>
-      </c>
-      <c r="S114" t="s">
         <v>47</v>
       </c>
-      <c r="T114" t="s">
-        <v>44</v>
+      <c r="X114" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="115">
@@ -3912,7 +3987,7 @@
         <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -3921,25 +3996,25 @@
         <v>3</v>
       </c>
       <c r="G115" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H115" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I115" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>39</v>
-      </c>
-      <c r="S115" t="s">
-        <v>74</v>
-      </c>
-      <c r="T115" t="s">
-        <v>88</v>
+        <v>44</v>
+      </c>
+      <c r="X115" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="116">
@@ -3950,7 +4025,7 @@
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -3959,13 +4034,13 @@
         <v>5</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H116" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I116" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117">
@@ -3976,7 +4051,7 @@
         <v>3</v>
       </c>
       <c r="C117" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3985,13 +4060,13 @@
         <v>10</v>
       </c>
       <c r="G117" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H117" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I117" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="118">
@@ -4002,7 +4077,7 @@
         <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4011,13 +4086,13 @@
         <v>10</v>
       </c>
       <c r="G118" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H118" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I118" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119">
@@ -4028,7 +4103,7 @@
         <v>3</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -4037,13 +4112,13 @@
         <v>9</v>
       </c>
       <c r="G119" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H119" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I119" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120">
@@ -4054,7 +4129,7 @@
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -4063,16 +4138,16 @@
         <v>9</v>
       </c>
       <c r="G120" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H120" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I120" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K120" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="121">
@@ -4083,7 +4158,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4092,25 +4167,25 @@
         <v>10</v>
       </c>
       <c r="G121" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J121">
         <v>9</v>
       </c>
       <c r="K121" t="s">
-        <v>42</v>
-      </c>
-      <c r="S121" t="s">
         <v>47</v>
       </c>
-      <c r="T121" t="s">
-        <v>48</v>
+      <c r="X121" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="122">
@@ -4121,7 +4196,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -4130,25 +4205,25 @@
         <v>2</v>
       </c>
       <c r="G122" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H122" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J122">
         <v>6</v>
       </c>
       <c r="K122" t="s">
-        <v>42</v>
-      </c>
-      <c r="S122" t="s">
-        <v>67</v>
-      </c>
-      <c r="T122" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X122" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="123">
@@ -4159,7 +4234,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4168,25 +4243,25 @@
         <v>10</v>
       </c>
       <c r="G123" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H123" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I123" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J123">
         <v>3</v>
       </c>
       <c r="K123" t="s">
-        <v>39</v>
-      </c>
-      <c r="S123" t="s">
-        <v>43</v>
-      </c>
-      <c r="T123" t="s">
-        <v>57</v>
+        <v>44</v>
+      </c>
+      <c r="X123" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="124">
@@ -4197,7 +4272,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -4206,25 +4281,25 @@
         <v>8</v>
       </c>
       <c r="G124" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H124" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I124" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>39</v>
-      </c>
-      <c r="S124" t="s">
-        <v>40</v>
-      </c>
-      <c r="T124" t="s">
-        <v>90</v>
+        <v>44</v>
+      </c>
+      <c r="X124" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="125">
@@ -4235,7 +4310,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D125">
         <v>3</v>
@@ -4244,25 +4319,25 @@
         <v>8</v>
       </c>
       <c r="G125" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H125" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I125" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J125">
         <v>3</v>
       </c>
       <c r="K125" t="s">
-        <v>42</v>
-      </c>
-      <c r="S125" t="s">
         <v>47</v>
       </c>
-      <c r="T125" t="s">
-        <v>66</v>
+      <c r="X125" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="126">
@@ -4273,7 +4348,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -4282,13 +4357,13 @@
         <v>6</v>
       </c>
       <c r="G126" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H126" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I126" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="127">
@@ -4299,7 +4374,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4308,13 +4383,13 @@
         <v>10</v>
       </c>
       <c r="G127" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H127" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I127" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
@@ -4325,7 +4400,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4334,13 +4409,13 @@
         <v>10</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H128" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I128" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="129">
@@ -4351,7 +4426,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -4360,13 +4435,13 @@
         <v>4</v>
       </c>
       <c r="G129" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H129" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I129" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130">
@@ -4377,7 +4452,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D130">
         <v>3</v>
@@ -4386,13 +4461,13 @@
         <v>4</v>
       </c>
       <c r="G130" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H130" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I130" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131">
@@ -4403,7 +4478,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D131">
         <v>4</v>
@@ -4412,13 +4487,13 @@
         <v>10</v>
       </c>
       <c r="G131" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H131" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I131" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132">
@@ -4429,7 +4504,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -4438,13 +4513,13 @@
         <v>10</v>
       </c>
       <c r="G132" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H132" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I132" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="133">
@@ -4455,7 +4530,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -4464,27 +4539,27 @@
         <v>10</v>
       </c>
       <c r="G133" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H133" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J133">
         <v>10</v>
       </c>
       <c r="K133" t="s">
-        <v>42</v>
-      </c>
-      <c r="S133" t="s">
         <v>47</v>
       </c>
-      <c r="T133" t="s">
-        <v>91</v>
-      </c>
-      <c r="W133">
+      <c r="X133" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB133">
         <v>12</v>
       </c>
     </row>
@@ -4496,7 +4571,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -4505,15 +4580,15 @@
         <v>10</v>
       </c>
       <c r="G134" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I134" t="s">
-        <v>65</v>
-      </c>
-      <c r="S134" t="s">
-        <v>71</v>
-      </c>
-      <c r="W134">
+        <v>70</v>
+      </c>
+      <c r="X134" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB134">
         <v>12</v>
       </c>
     </row>
@@ -4525,7 +4600,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4534,27 +4609,27 @@
         <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I135" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J135">
         <v>13</v>
       </c>
       <c r="K135" t="s">
-        <v>42</v>
-      </c>
-      <c r="S135" t="s">
         <v>47</v>
       </c>
-      <c r="T135" t="s">
-        <v>66</v>
-      </c>
-      <c r="W135">
+      <c r="X135" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB135">
         <v>12</v>
       </c>
     </row>
@@ -4566,7 +4641,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D136">
         <v>2</v>
@@ -4575,25 +4650,25 @@
         <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H136" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I136" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J136">
         <v>13</v>
       </c>
       <c r="K136" t="s">
-        <v>42</v>
-      </c>
-      <c r="S136" t="s">
         <v>47</v>
       </c>
-      <c r="T136" t="s">
-        <v>57</v>
+      <c r="X136" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="137">
@@ -4604,7 +4679,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -4613,25 +4688,25 @@
         <v>10</v>
       </c>
       <c r="G137" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H137" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I137" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J137">
         <v>8</v>
       </c>
       <c r="K137" t="s">
-        <v>42</v>
-      </c>
-      <c r="S137" t="s">
-        <v>67</v>
-      </c>
-      <c r="T137" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="X137" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="138">
@@ -4642,7 +4717,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -4651,25 +4726,25 @@
         <v>1</v>
       </c>
       <c r="G138" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H138" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I138" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J138">
         <v>6</v>
       </c>
       <c r="K138" t="s">
-        <v>42</v>
-      </c>
-      <c r="S138" t="s">
         <v>47</v>
       </c>
-      <c r="T138" t="s">
-        <v>91</v>
+      <c r="X138" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="139">
@@ -4680,7 +4755,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4689,27 +4764,27 @@
         <v>4</v>
       </c>
       <c r="G139" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I139" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>39</v>
-      </c>
-      <c r="S139" t="s">
-        <v>47</v>
-      </c>
-      <c r="T139" t="s">
-        <v>83</v>
-      </c>
-      <c r="W139">
+        <v>44</v>
+      </c>
+      <c r="X139" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB139">
         <v>12</v>
       </c>
     </row>
@@ -4721,7 +4796,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -4730,27 +4805,27 @@
         <v>7</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H140" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I140" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J140">
         <v>-10</v>
       </c>
       <c r="K140" t="s">
-        <v>39</v>
-      </c>
-      <c r="S140" t="s">
-        <v>47</v>
-      </c>
-      <c r="T140" t="s">
-        <v>57</v>
-      </c>
-      <c r="W140">
+        <v>44</v>
+      </c>
+      <c r="X140" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB140">
         <v>12</v>
       </c>
     </row>
@@ -4762,7 +4837,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -4771,27 +4846,30 @@
         <v>17</v>
       </c>
       <c r="G141" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H141" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I141" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J141">
         <v>6</v>
       </c>
       <c r="K141" t="s">
-        <v>42</v>
-      </c>
-      <c r="S141" t="s">
-        <v>40</v>
-      </c>
-      <c r="T141" t="s">
-        <v>59</v>
-      </c>
-      <c r="W141">
+        <v>47</v>
+      </c>
+      <c r="P141" t="s">
+        <v>29</v>
+      </c>
+      <c r="X141" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB141">
         <v>12</v>
       </c>
     </row>
@@ -4803,7 +4881,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D142">
         <v>3</v>
@@ -4812,25 +4890,25 @@
         <v>12</v>
       </c>
       <c r="G142" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H142" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>39</v>
-      </c>
-      <c r="S142" t="s">
-        <v>47</v>
-      </c>
-      <c r="T142" t="s">
         <v>44</v>
+      </c>
+      <c r="X142" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="143">
@@ -4841,7 +4919,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D143">
         <v>4</v>
@@ -4850,13 +4928,13 @@
         <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H143" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I143" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="144">
@@ -4867,7 +4945,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -4876,13 +4954,13 @@
         <v>10</v>
       </c>
       <c r="G144" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H144" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I144" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145">
@@ -4893,7 +4971,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4902,13 +4980,13 @@
         <v>10</v>
       </c>
       <c r="G145" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H145" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I145" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146">
@@ -4919,7 +4997,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -4928,13 +5006,13 @@
         <v>10</v>
       </c>
       <c r="G146" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H146" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I146" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147">
@@ -4945,7 +5023,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -4954,13 +5032,13 @@
         <v>1</v>
       </c>
       <c r="G147" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H147" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I147" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148">
@@ -4971,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D148">
         <v>4</v>
@@ -4980,13 +5058,13 @@
         <v>4</v>
       </c>
       <c r="G148" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H148" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I148" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149">
@@ -4997,7 +5075,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5006,25 +5084,25 @@
         <v>10</v>
       </c>
       <c r="G149" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H149" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I149" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J149">
         <v>6</v>
       </c>
       <c r="K149" t="s">
-        <v>42</v>
-      </c>
-      <c r="S149" t="s">
         <v>47</v>
       </c>
-      <c r="T149" t="s">
-        <v>83</v>
+      <c r="X149" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="150">
@@ -5035,7 +5113,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -5044,25 +5122,25 @@
         <v>4</v>
       </c>
       <c r="G150" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H150" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I150" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J150">
         <v>4</v>
       </c>
       <c r="K150" t="s">
-        <v>42</v>
-      </c>
-      <c r="S150" t="s">
         <v>47</v>
       </c>
-      <c r="T150" t="s">
-        <v>83</v>
+      <c r="X150" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="151">
@@ -5073,7 +5151,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -5082,25 +5160,25 @@
         <v>10</v>
       </c>
       <c r="G151" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H151" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I151" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J151">
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>39</v>
-      </c>
-      <c r="S151" t="s">
-        <v>47</v>
-      </c>
-      <c r="T151" t="s">
-        <v>83</v>
+        <v>44</v>
+      </c>
+      <c r="X151" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
